--- a/src/width_txt/Максимальные_значения_делителя_АЦП_№2.xlsx
+++ b/src/width_txt/Максимальные_значения_делителя_АЦП_№2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="185" uniqueCount="5">
   <si>
     <t>Row</t>
   </si>
@@ -101,13 +101,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>12824029397</v>
+        <v>67035140184</v>
       </c>
       <c r="C2" s="0">
-        <v>160350135</v>
+        <v>67035140184</v>
       </c>
       <c r="D2" s="0">
-        <v>214779.8842105263</v>
+        <v>18421411</v>
       </c>
     </row>
   </sheetData>
